--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{543A262B-DDEA-4D15-802F-4CDD9E98D923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6B7CC6F-6F43-4732-9001-FCC5C0D3A1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -163,8 +163,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -237,7 +237,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -245,12 +245,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -600,7 +600,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -626,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1912</v>
+        <v>1894</v>
       </c>
       <c r="C3" s="3">
-        <v>2126</v>
+        <v>2197</v>
       </c>
       <c r="D3" s="3">
-        <v>1710.52</v>
+        <v>1803.71</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -643,16 +643,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1937.96</v>
+        <v>1976.42</v>
       </c>
       <c r="C4" s="3">
-        <v>2254.2399999999998</v>
+        <v>2290.4499999999998</v>
       </c>
       <c r="D4" s="3">
-        <v>1438.9</v>
+        <v>1553.9</v>
       </c>
       <c r="E4" s="3">
-        <v>553.77</v>
+        <v>585.87</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -664,16 +664,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1571.2</v>
+        <v>1620.4</v>
       </c>
       <c r="C5" s="3">
-        <v>1812.9</v>
+        <v>1856.3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>642.5</v>
+        <v>663.4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,10 +681,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="C6" s="3">
-        <v>1908</v>
+        <v>1920</v>
       </c>
       <c r="D6" s="3">
         <v>1580</v>
@@ -694,7 +694,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -702,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1632.28</v>
+        <v>1649.55</v>
       </c>
       <c r="C7" s="3">
-        <v>1894.53</v>
+        <v>1915.1</v>
       </c>
       <c r="D7" s="3">
-        <v>1520.38</v>
+        <v>1549.03</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -721,18 +721,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1806.3396288796134</v>
+        <v>1827.7352432699431</v>
       </c>
       <c r="C8" s="3">
-        <v>1958.4659255279582</v>
+        <v>1990.8619412200542</v>
       </c>
       <c r="D8" s="3">
-        <v>1477.9518122081251</v>
+        <v>1508.2736478142749</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>897.30131834524946</v>
+        <v>893.38931423396718</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2631.5789473684213</v>
+        <v>2564.4455740906719</v>
       </c>
       <c r="C9" s="3">
-        <v>2434.9129050383967</v>
+        <v>2501.5718432705044</v>
       </c>
       <c r="D9" s="3">
-        <v>2395.9810558424533</v>
+        <v>2462.6436397201451</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -757,18 +757,18 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1812</v>
+        <v>1914</v>
       </c>
       <c r="C10" s="3">
-        <v>1922</v>
+        <v>2065</v>
       </c>
       <c r="D10" s="3">
-        <v>1442</v>
+        <v>1601</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>969</v>
+        <v>986</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -776,13 +776,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2323.150000000001</v>
+        <v>2316.8095238095248</v>
       </c>
       <c r="C11" s="3">
-        <v>2477.8500000000004</v>
+        <v>2505.4499999999998</v>
       </c>
       <c r="D11" s="3">
-        <v>1989.86958333333</v>
+        <v>2088.0944444444444</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -793,18 +793,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2114.94</v>
+        <v>2172.33</v>
       </c>
       <c r="C12" s="3">
-        <v>2257.13</v>
+        <v>2290.7399999999998</v>
       </c>
       <c r="D12" s="3">
-        <v>1792.48</v>
+        <v>1853.52</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1015.4</v>
+        <v>1012.97</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -812,18 +812,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2331</v>
+        <v>2357</v>
       </c>
       <c r="C13" s="3">
-        <v>2328</v>
+        <v>2426</v>
       </c>
       <c r="D13" s="3">
-        <v>1520.9</v>
+        <v>1683</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1089</v>
+        <v>1086.5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2093</v>
+        <v>2158</v>
       </c>
       <c r="C14" s="3">
-        <v>2054</v>
+        <v>2122</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -848,20 +848,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1643.6321619247865</v>
+        <v>1713.9251525215382</v>
       </c>
       <c r="C15" s="3">
-        <v>1864.4119750966993</v>
+        <v>1918.9583555393458</v>
       </c>
       <c r="D15" s="3">
-        <v>1864.4119750966993</v>
+        <v>1918.9583555393458</v>
       </c>
       <c r="E15" s="3">
-        <v>1093.3920704845816</v>
+        <v>1410.724550406482</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>977.65579419721996</v>
+        <v>966.37282311747686</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,13 +869,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1854.6</v>
+        <v>1894.2</v>
       </c>
       <c r="C16" s="3">
-        <v>1953.8</v>
+        <v>1989.3</v>
       </c>
       <c r="D16" s="3">
-        <v>1410.55</v>
+        <v>1517.55</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -886,20 +886,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2034.68</v>
+        <v>2084.09</v>
       </c>
       <c r="C17" s="3">
-        <v>2141.8200000000002</v>
+        <v>2190.6799999999998</v>
       </c>
       <c r="D17" s="3">
-        <v>1964.95</v>
+        <v>2051.85</v>
       </c>
       <c r="E17" s="3">
-        <v>670.36</v>
+        <v>702.18</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>769.04</v>
+        <v>771.22</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -907,18 +907,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1939.2</v>
+        <v>1975.8</v>
       </c>
       <c r="C18" s="3">
-        <v>2047.67</v>
+        <v>2096.17</v>
       </c>
       <c r="D18" s="3">
-        <v>1731.86</v>
+        <v>1780.36</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>911.67</v>
+        <v>914.75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,18 +926,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1883.98</v>
+        <v>1917.66</v>
       </c>
       <c r="C19" s="3">
-        <v>2128.2399999999998</v>
+        <v>2184.3000000000002</v>
       </c>
       <c r="D19" s="3">
-        <v>1472.26</v>
+        <v>1564.37</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>770.33</v>
+        <v>786.55</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -945,18 +945,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1868</v>
+        <v>1793</v>
       </c>
       <c r="C20" s="3">
-        <v>2024</v>
+        <v>2123</v>
       </c>
       <c r="D20" s="3">
-        <v>1510</v>
+        <v>1610</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>738</v>
+        <v>792</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -981,16 +981,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2465.83</v>
+        <v>2433.52</v>
       </c>
       <c r="C22" s="3">
-        <v>2442.2399999999998</v>
+        <v>2494.1999999999998</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>931.1</v>
+        <v>935.72</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,22 +998,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1811.6151270136215</v>
+        <v>1821.8215669676083</v>
       </c>
       <c r="C23" s="3">
-        <v>1982.0406158447261</v>
+        <v>2005.146659141315</v>
       </c>
       <c r="D23" s="3">
-        <v>1577.9070023665197</v>
+        <v>1645.4784256489672</v>
       </c>
       <c r="E23" s="3">
-        <v>744.57448607040601</v>
+        <v>806.19888024892975</v>
       </c>
       <c r="F23" s="3">
-        <v>592.83218171485248</v>
+        <v>601.07699515430829</v>
       </c>
       <c r="G23" s="3">
-        <v>686.86402384551252</v>
+        <v>697.9876037646942</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,20 +1021,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>2093</v>
+        <v>2072</v>
       </c>
       <c r="C24" s="3">
-        <v>2104</v>
+        <v>2152</v>
       </c>
       <c r="D24" s="3">
-        <v>2114</v>
+        <v>2185</v>
       </c>
       <c r="E24" s="3">
-        <v>1048</v>
+        <v>1067.58</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,20 +1042,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1851.3147622765096</v>
+        <v>1888.8411200730482</v>
       </c>
       <c r="C25" s="3">
-        <v>1941.5087872960264</v>
+        <v>1999.6937300258712</v>
       </c>
       <c r="D25" s="3">
-        <v>1416.4321483653537</v>
+        <v>1494.4376807183078</v>
       </c>
       <c r="E25" s="3">
-        <v>844.53245492107612</v>
+        <v>909.19570841576626</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>890.41299339286729</v>
+        <v>892.78268147922699</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1063,16 +1063,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1774</v>
+        <v>1808</v>
       </c>
       <c r="C26" s="3">
-        <v>1908</v>
+        <v>1924</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1080,18 +1080,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1633.44</v>
+        <v>1640.9925284276001</v>
       </c>
       <c r="C27" s="3">
-        <v>1879.92</v>
+        <v>1853.9495283472843</v>
       </c>
       <c r="D27" s="3">
-        <v>1491.4</v>
+        <v>1521.731896330378</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>994.83</v>
+        <v>990.01493145250447</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,20 +1099,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1815.9729689999999</v>
+        <v>1866.892601</v>
       </c>
       <c r="C28" s="3">
-        <v>1795.450398</v>
+        <v>1834.0250719999999</v>
       </c>
       <c r="D28" s="3">
-        <v>1396.2440000000001</v>
+        <v>1405.09</v>
       </c>
       <c r="E28" s="3">
-        <v>624.39700000000005</v>
+        <v>646.76</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1088.8231500000002</v>
+        <v>1097.504964</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1120,16 +1120,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1587.6187063250313</v>
+        <v>1513.6955943622017</v>
       </c>
       <c r="C29" s="3">
-        <v>1904.0494535029563</v>
+        <v>1980.9414059037317</v>
       </c>
       <c r="D29" s="3">
-        <v>1765.0062712775489</v>
+        <v>1809.9459267795407</v>
       </c>
       <c r="E29" s="3">
-        <v>1008.4214298512811</v>
+        <v>1032.2666430281004</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1139,22 +1139,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>2041.6684660061321</v>
+        <v>2063.3575051911107</v>
       </c>
       <c r="C30" s="5">
-        <v>2107.3855574757486</v>
+        <v>2158.7361941679264</v>
       </c>
       <c r="D30" s="5">
-        <v>1595.2382987100923</v>
+        <v>1711.5895290393926</v>
       </c>
       <c r="E30" s="5">
-        <v>668.18125247344585</v>
+        <v>688.25140902956775</v>
       </c>
       <c r="F30" s="5">
-        <v>570.53539611938243</v>
+        <v>578.47011701797373</v>
       </c>
       <c r="G30" s="5">
-        <v>850.28188678964614</v>
+        <v>854.24697507653673</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1162,20 +1162,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2099.8495948841119</v>
+        <v>2127.7075745994816</v>
       </c>
       <c r="C31" s="5">
-        <v>2137.6925501645705</v>
+        <v>2191.7808937568138</v>
       </c>
       <c r="D31" s="5">
-        <v>1578.7497009047352</v>
+        <v>1697.7483721631434</v>
       </c>
       <c r="E31" s="5">
-        <v>688.06590904759287</v>
+        <v>708.97087071283522</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>888.79971866615824</v>
+        <v>891.1587906294244</v>
       </c>
     </row>
   </sheetData>
